--- a/upload/database.xlsx
+++ b/upload/database.xlsx
@@ -1,51 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\Medics-Ecommerce-Platform\upload\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50456EE9-7AE6-445E-8E8D-D10404F50EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="orders" sheetId="1" r:id="rId1"/>
-    <sheet name="returns" sheetId="2" r:id="rId2"/>
-    <sheet name="charges" sheetId="3" r:id="rId3"/>
-    <sheet name="cod" sheetId="4" r:id="rId4"/>
-    <sheet name="disputes" sheetId="5" r:id="rId5"/>
-    <sheet name="expenses" sheetId="6" r:id="rId6"/>
-    <sheet name="inventory" sheetId="7" r:id="rId7"/>
-    <sheet name="revenue" sheetId="8" r:id="rId8"/>
-    <sheet name="pl" sheetId="9" r:id="rId9"/>
-    <sheet name="tax" sheetId="10" r:id="rId10"/>
-    <sheet name="balance_sheet" sheetId="11" r:id="rId11"/>
-    <sheet name="reports" sheetId="12" r:id="rId12"/>
+    <sheet name="orders" sheetId="1" r:id="rId4"/>
+    <sheet name="returns" sheetId="2" r:id="rId5"/>
+    <sheet name="charges" sheetId="3" r:id="rId6"/>
+    <sheet name="cod" sheetId="4" r:id="rId7"/>
+    <sheet name="disputes" sheetId="5" r:id="rId8"/>
+    <sheet name="expenses" sheetId="6" r:id="rId9"/>
+    <sheet name="inventory" sheetId="7" r:id="rId10"/>
+    <sheet name="revenue" sheetId="8" r:id="rId11"/>
+    <sheet name="pl" sheetId="9" r:id="rId12"/>
+    <sheet name="tax" sheetId="10" r:id="rId13"/>
+    <sheet name="balance_sheet" sheetId="11" r:id="rId14"/>
+    <sheet name="reports" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">balance_sheet!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">charges!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">cod!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">disputes!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">expenses!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">inventory!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">orders!$A$1:$P$284</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">pl!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">reports!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">returns!$A$1:$N$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">revenue!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">tax!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'orders'!$A$1:$P$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'returns'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'charges'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'cod'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'disputes'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'expenses'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'inventory'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'revenue'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'pl'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'tax'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'balance_sheet'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'reports'!$A$1:$E$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4831" uniqueCount="1477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1477">
   <si>
     <t>Tracking No</t>
   </si>
@@ -179,6 +173,9 @@
     <t>PKR 8,500</t>
   </si>
   <si>
+    <t>Returned</t>
+  </si>
+  <si>
     <t>MP05500267</t>
   </si>
   <si>
@@ -198,9 +195,6 @@
   </si>
   <si>
     <t>PKR 800</t>
-  </si>
-  <si>
-    <t>Returned</t>
   </si>
   <si>
     <t>M&amp;P</t>
@@ -4481,15 +4475,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -4579,43 +4581,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="8" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="9" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -4905,27 +4899,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:P285"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.140625" customWidth="1"/>
-    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="true" style="0"/>
+    <col min="2" max="2" width="16.42578125" customWidth="true" style="0"/>
+    <col min="3" max="3" width="12.85546875" customWidth="true" style="0"/>
+    <col min="4" max="4" width="18.7109375" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.85546875" customWidth="true" style="0"/>
+    <col min="6" max="6" width="36.42578125" customWidth="true" style="0"/>
+    <col min="7" max="7" width="9.28515625" customWidth="true" style="0"/>
+    <col min="8" max="8" width="9.28515625" customWidth="true" style="0"/>
+    <col min="9" max="9" width="24.7109375" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.7109375" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.7109375" customWidth="true" style="0"/>
+    <col min="12" max="12" width="17.5703125" customWidth="true" style="0"/>
+    <col min="13" max="13" width="22.140625" customWidth="true" style="0"/>
+    <col min="14" max="14" width="14" customWidth="true" style="0"/>
+    <col min="15" max="15" width="21.140625" customWidth="true" style="0"/>
+    <col min="16" max="16" width="18.7109375" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" customHeight="1" ht="21.95">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4975,7 +4974,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -5022,7 +5021,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -5070,7 +5069,7 @@
       </c>
       <c r="P3" s="2"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -5108,7 +5107,7 @@
         <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="N4" t="s">
         <v>25</v>
@@ -5117,27 +5116,27 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5" s="2">
         <v>1</v>
@@ -5152,10 +5151,10 @@
         <v>0.2</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>52</v>
@@ -5165,7 +5164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -5179,7 +5178,7 @@
         <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
         <v>56</v>
@@ -5203,7 +5202,7 @@
         <v>58</v>
       </c>
       <c r="M6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="N6" t="s">
         <v>25</v>
@@ -5212,7 +5211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16">
       <c r="A7" s="2" t="s">
         <v>59</v>
       </c>
@@ -5260,7 +5259,7 @@
       </c>
       <c r="P7" s="2"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -5274,7 +5273,7 @@
         <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
         <v>68</v>
@@ -5304,7 +5303,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16">
       <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
@@ -5318,7 +5317,7 @@
         <v>75</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
@@ -5350,7 +5349,7 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
         <v>80</v>
       </c>
@@ -5394,7 +5393,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16">
       <c r="A11" s="2" t="s">
         <v>86</v>
       </c>
@@ -5440,7 +5439,7 @@
       </c>
       <c r="P11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -5487,7 +5486,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
         <v>101</v>
       </c>
@@ -5535,7 +5534,7 @@
       </c>
       <c r="P13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -5579,7 +5578,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16">
       <c r="A15" s="2" t="s">
         <v>112</v>
       </c>
@@ -5627,7 +5626,7 @@
       </c>
       <c r="P15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -5665,7 +5664,7 @@
         <v>58</v>
       </c>
       <c r="M16" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N16" t="s">
         <v>25</v>
@@ -5674,7 +5673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16">
       <c r="A17" s="2" t="s">
         <v>122</v>
       </c>
@@ -5722,7 +5721,7 @@
       </c>
       <c r="P17" s="2"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>128</v>
       </c>
@@ -5766,7 +5765,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16">
       <c r="A19" s="2" t="s">
         <v>134</v>
       </c>
@@ -5780,7 +5779,7 @@
         <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
@@ -5814,7 +5813,7 @@
       </c>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>138</v>
       </c>
@@ -5861,7 +5860,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16">
       <c r="A21" s="2" t="s">
         <v>144</v>
       </c>
@@ -5905,7 +5904,7 @@
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>150</v>
       </c>
@@ -5952,7 +5951,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16">
       <c r="A23" s="2" t="s">
         <v>155</v>
       </c>
@@ -5966,7 +5965,7 @@
         <v>88</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>157</v>
@@ -5990,7 +5989,7 @@
         <v>159</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>25</v>
@@ -6000,7 +5999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
         <v>160</v>
       </c>
@@ -6047,7 +6046,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16">
       <c r="A25" s="2" t="s">
         <v>164</v>
       </c>
@@ -6061,7 +6060,7 @@
         <v>141</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>31</v>
@@ -6095,7 +6094,7 @@
       </c>
       <c r="P25" s="2"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>166</v>
       </c>
@@ -6109,7 +6108,7 @@
         <v>168</v>
       </c>
       <c r="E26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" t="s">
         <v>169</v>
@@ -6130,7 +6129,7 @@
         <v>1.5</v>
       </c>
       <c r="M26" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N26" t="s">
         <v>34</v>
@@ -6139,7 +6138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16">
       <c r="A27" s="2" t="s">
         <v>171</v>
       </c>
@@ -6187,7 +6186,7 @@
       </c>
       <c r="P27" s="2"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>176</v>
       </c>
@@ -6231,7 +6230,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16">
       <c r="A29" s="2" t="s">
         <v>182</v>
       </c>
@@ -6277,7 +6276,7 @@
       </c>
       <c r="P29" s="2"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
         <v>185</v>
       </c>
@@ -6321,7 +6320,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16">
       <c r="A31" s="2" t="s">
         <v>187</v>
       </c>
@@ -6369,7 +6368,7 @@
       </c>
       <c r="P31" s="2"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>191</v>
       </c>
@@ -6413,7 +6412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16">
       <c r="A33" s="2" t="s">
         <v>195</v>
       </c>
@@ -6430,10 +6429,10 @@
         <v>124</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H33" s="2">
         <v>3</v>
@@ -6459,7 +6458,7 @@
       </c>
       <c r="P33" s="2"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>198</v>
       </c>
@@ -6497,7 +6496,7 @@
         <v>201</v>
       </c>
       <c r="M34" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N34" t="s">
         <v>25</v>
@@ -6506,7 +6505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16">
       <c r="A35" s="2" t="s">
         <v>202</v>
       </c>
@@ -6517,7 +6516,7 @@
         <v>200</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>40</v>
@@ -6544,7 +6543,7 @@
         <v>204</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>25</v>
@@ -6554,7 +6553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>205</v>
       </c>
@@ -6568,7 +6567,7 @@
         <v>207</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F36" t="s">
         <v>76</v>
@@ -6601,7 +6600,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16">
       <c r="A37" s="2" t="s">
         <v>208</v>
       </c>
@@ -6647,7 +6646,7 @@
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>212</v>
       </c>
@@ -6694,7 +6693,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16">
       <c r="A39" s="2" t="s">
         <v>215</v>
       </c>
@@ -6708,7 +6707,7 @@
         <v>217</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>157</v>
@@ -6740,7 +6739,7 @@
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>219</v>
       </c>
@@ -6754,7 +6753,7 @@
         <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F40" t="s">
         <v>125</v>
@@ -6787,7 +6786,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16">
       <c r="A41" s="2" t="s">
         <v>221</v>
       </c>
@@ -6801,7 +6800,7 @@
         <v>197</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>223</v>
@@ -6835,7 +6834,7 @@
       </c>
       <c r="P41" s="2"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>226</v>
       </c>
@@ -6882,7 +6881,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16">
       <c r="A43" s="2" t="s">
         <v>229</v>
       </c>
@@ -6928,7 +6927,7 @@
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>232</v>
       </c>
@@ -6942,7 +6941,7 @@
         <v>235</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F44" t="s">
         <v>97</v>
@@ -6975,7 +6974,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16">
       <c r="A45" s="2" t="s">
         <v>236</v>
       </c>
@@ -7023,7 +7022,7 @@
       </c>
       <c r="P45" s="2"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>240</v>
       </c>
@@ -7070,7 +7069,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16">
       <c r="A47" s="2" t="s">
         <v>246</v>
       </c>
@@ -7116,7 +7115,7 @@
       </c>
       <c r="P47" s="2"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>249</v>
       </c>
@@ -7163,7 +7162,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16">
       <c r="A49" s="2" t="s">
         <v>254</v>
       </c>
@@ -7177,7 +7176,7 @@
         <v>141</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>76</v>
@@ -7201,7 +7200,7 @@
         <v>137</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>25</v>
@@ -7211,7 +7210,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
         <v>256</v>
       </c>
@@ -7255,7 +7254,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16">
       <c r="A51" s="2" t="s">
         <v>259</v>
       </c>
@@ -7272,10 +7271,10 @@
         <v>40</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H51" s="2">
         <v>3</v>
@@ -7301,7 +7300,7 @@
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
         <v>263</v>
       </c>
@@ -7348,7 +7347,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16">
       <c r="A53" s="2" t="s">
         <v>268</v>
       </c>
@@ -7362,7 +7361,7 @@
         <v>189</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>21</v>
@@ -7396,7 +7395,7 @@
       </c>
       <c r="P53" s="2"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>271</v>
       </c>
@@ -7410,7 +7409,7 @@
         <v>55</v>
       </c>
       <c r="E54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F54" t="s">
         <v>76</v>
@@ -7443,7 +7442,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16">
       <c r="A55" s="2" t="s">
         <v>273</v>
       </c>
@@ -7491,7 +7490,7 @@
       </c>
       <c r="P55" s="2"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
         <v>276</v>
       </c>
@@ -7535,7 +7534,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16">
       <c r="A57" s="2" t="s">
         <v>278</v>
       </c>
@@ -7581,7 +7580,7 @@
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16">
       <c r="A58" t="s">
         <v>282</v>
       </c>
@@ -7595,7 +7594,7 @@
         <v>163</v>
       </c>
       <c r="E58" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F58" t="s">
         <v>83</v>
@@ -7628,7 +7627,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16">
       <c r="A59" s="2" t="s">
         <v>286</v>
       </c>
@@ -7676,7 +7675,7 @@
       </c>
       <c r="P59" s="2"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
         <v>288</v>
       </c>
@@ -7690,7 +7689,7 @@
         <v>147</v>
       </c>
       <c r="E60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F60" t="s">
         <v>179</v>
@@ -7723,7 +7722,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16">
       <c r="A61" s="2" t="s">
         <v>290</v>
       </c>
@@ -7771,7 +7770,7 @@
       </c>
       <c r="P61" s="2"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16">
       <c r="A62" t="s">
         <v>293</v>
       </c>
@@ -7785,7 +7784,7 @@
         <v>163</v>
       </c>
       <c r="E62" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F62" t="s">
         <v>56</v>
@@ -7818,7 +7817,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16">
       <c r="A63" s="2" t="s">
         <v>295</v>
       </c>
@@ -7829,7 +7828,7 @@
         <v>297</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>40</v>
@@ -7866,7 +7865,7 @@
       </c>
       <c r="P63" s="2"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16">
       <c r="A64" t="s">
         <v>298</v>
       </c>
@@ -7910,7 +7909,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16">
       <c r="A65" s="2" t="s">
         <v>301</v>
       </c>
@@ -7958,7 +7957,7 @@
       </c>
       <c r="P65" s="2"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
         <v>303</v>
       </c>
@@ -7969,7 +7968,7 @@
         <v>305</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E66" t="s">
         <v>124</v>
@@ -8005,7 +8004,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16">
       <c r="A67" s="2" t="s">
         <v>306</v>
       </c>
@@ -8053,7 +8052,7 @@
       </c>
       <c r="P67" s="2"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16">
       <c r="A68" t="s">
         <v>309</v>
       </c>
@@ -8067,7 +8066,7 @@
         <v>312</v>
       </c>
       <c r="E68" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F68" t="s">
         <v>223</v>
@@ -8100,7 +8099,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16">
       <c r="A69" s="2" t="s">
         <v>315</v>
       </c>
@@ -8114,7 +8113,7 @@
         <v>67</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>179</v>
@@ -8148,7 +8147,7 @@
       </c>
       <c r="P69" s="2"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16">
       <c r="A70" t="s">
         <v>317</v>
       </c>
@@ -8195,7 +8194,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16">
       <c r="A71" s="2" t="s">
         <v>320</v>
       </c>
@@ -8209,7 +8208,7 @@
         <v>109</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>90</v>
@@ -8233,7 +8232,7 @@
         <v>322</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>25</v>
@@ -8243,7 +8242,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
         <v>323</v>
       </c>
@@ -8290,7 +8289,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16">
       <c r="A73" s="2" t="s">
         <v>325</v>
       </c>
@@ -8307,10 +8306,10 @@
         <v>30</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H73" s="2">
         <v>3</v>
@@ -8338,7 +8337,7 @@
       </c>
       <c r="P73" s="2"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
         <v>328</v>
       </c>
@@ -8352,7 +8351,7 @@
         <v>88</v>
       </c>
       <c r="E74" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F74" t="s">
         <v>148</v>
@@ -8382,7 +8381,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16">
       <c r="A75" s="2" t="s">
         <v>330</v>
       </c>
@@ -8430,7 +8429,7 @@
       </c>
       <c r="P75" s="2"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
         <v>333</v>
       </c>
@@ -8477,7 +8476,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16">
       <c r="A77" s="2" t="s">
         <v>335</v>
       </c>
@@ -8491,7 +8490,7 @@
         <v>75</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>76</v>
@@ -8525,7 +8524,7 @@
       </c>
       <c r="P77" s="2"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
         <v>337</v>
       </c>
@@ -8566,7 +8565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16">
       <c r="A79" s="2" t="s">
         <v>339</v>
       </c>
@@ -8580,7 +8579,7 @@
         <v>39</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>243</v>
@@ -8614,7 +8613,7 @@
       </c>
       <c r="P79" s="2"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
         <v>343</v>
       </c>
@@ -8661,7 +8660,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16">
       <c r="A81" s="2" t="s">
         <v>345</v>
       </c>
@@ -8707,7 +8706,7 @@
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16">
       <c r="A82" t="s">
         <v>349</v>
       </c>
@@ -8745,7 +8744,7 @@
         <v>322</v>
       </c>
       <c r="M82" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N82" t="s">
         <v>25</v>
@@ -8754,7 +8753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16">
       <c r="A83" s="2" t="s">
         <v>352</v>
       </c>
@@ -8800,7 +8799,7 @@
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16">
       <c r="A84" t="s">
         <v>355</v>
       </c>
@@ -8847,7 +8846,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16">
       <c r="A85" s="2" t="s">
         <v>358</v>
       </c>
@@ -8895,7 +8894,7 @@
       </c>
       <c r="P85" s="2"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16">
       <c r="A86" t="s">
         <v>360</v>
       </c>
@@ -8939,7 +8938,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16">
       <c r="A87" s="2" t="s">
         <v>362</v>
       </c>
@@ -8987,7 +8986,7 @@
       </c>
       <c r="P87" s="2"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16">
       <c r="A88" t="s">
         <v>366</v>
       </c>
@@ -9028,7 +9027,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16">
       <c r="A89" s="2" t="s">
         <v>368</v>
       </c>
@@ -9042,7 +9041,7 @@
         <v>235</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>21</v>
@@ -9076,7 +9075,7 @@
       </c>
       <c r="P89" s="2"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16">
       <c r="A90" t="s">
         <v>371</v>
       </c>
@@ -9123,7 +9122,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16">
       <c r="A91" s="2" t="s">
         <v>374</v>
       </c>
@@ -9137,7 +9136,7 @@
         <v>238</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>41</v>
@@ -9169,7 +9168,7 @@
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16">
       <c r="A92" t="s">
         <v>376</v>
       </c>
@@ -9213,7 +9212,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16">
       <c r="A93" s="2" t="s">
         <v>379</v>
       </c>
@@ -9251,7 +9250,7 @@
         <v>266</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>25</v>
@@ -9261,7 +9260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16">
       <c r="A94" t="s">
         <v>382</v>
       </c>
@@ -9275,7 +9274,7 @@
         <v>327</v>
       </c>
       <c r="E94" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F94" t="s">
         <v>97</v>
@@ -9308,7 +9307,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16">
       <c r="A95" s="2" t="s">
         <v>384</v>
       </c>
@@ -9354,7 +9353,7 @@
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16">
       <c r="A96" t="s">
         <v>386</v>
       </c>
@@ -9398,7 +9397,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16">
       <c r="A97" s="2" t="s">
         <v>391</v>
       </c>
@@ -9446,7 +9445,7 @@
       </c>
       <c r="P97" s="2"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16">
       <c r="A98" t="s">
         <v>394</v>
       </c>
@@ -9493,7 +9492,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16">
       <c r="A99" s="2" t="s">
         <v>397</v>
       </c>
@@ -9541,7 +9540,7 @@
       </c>
       <c r="P99" s="2"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16">
       <c r="A100" t="s">
         <v>399</v>
       </c>
@@ -9576,7 +9575,7 @@
         <v>0.6</v>
       </c>
       <c r="M100" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N100" t="s">
         <v>25</v>
@@ -9585,7 +9584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16">
       <c r="A101" s="2" t="s">
         <v>401</v>
       </c>
@@ -9631,7 +9630,7 @@
       <c r="O101" s="2"/>
       <c r="P101" s="2"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16">
       <c r="A102" t="s">
         <v>405</v>
       </c>
@@ -9675,7 +9674,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16">
       <c r="A103" s="2" t="s">
         <v>408</v>
       </c>
@@ -9713,7 +9712,7 @@
         <v>342</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>34</v>
@@ -9723,7 +9722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16">
       <c r="A104" t="s">
         <v>410</v>
       </c>
@@ -9770,7 +9769,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16">
       <c r="A105" s="2" t="s">
         <v>413</v>
       </c>
@@ -9818,7 +9817,7 @@
       </c>
       <c r="P105" s="2"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16">
       <c r="A106" t="s">
         <v>415</v>
       </c>
@@ -9832,7 +9831,7 @@
         <v>39</v>
       </c>
       <c r="E106" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F106" t="s">
         <v>21</v>
@@ -9862,7 +9861,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16">
       <c r="A107" s="2" t="s">
         <v>417</v>
       </c>
@@ -9910,7 +9909,7 @@
       </c>
       <c r="P107" s="2"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16">
       <c r="A108" t="s">
         <v>421</v>
       </c>
@@ -9957,7 +9956,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16">
       <c r="A109" s="2" t="s">
         <v>423</v>
       </c>
@@ -10005,7 +10004,7 @@
       </c>
       <c r="P109" s="2"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16">
       <c r="A110" t="s">
         <v>425</v>
       </c>
@@ -10052,7 +10051,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16">
       <c r="A111" s="2" t="s">
         <v>429</v>
       </c>
@@ -10066,7 +10065,7 @@
         <v>189</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>31</v>
@@ -10100,7 +10099,7 @@
       </c>
       <c r="P111" s="2"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16">
       <c r="A112" t="s">
         <v>431</v>
       </c>
@@ -10147,7 +10146,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16">
       <c r="A113" s="2" t="s">
         <v>435</v>
       </c>
@@ -10193,7 +10192,7 @@
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16">
       <c r="A114" t="s">
         <v>438</v>
       </c>
@@ -10207,7 +10206,7 @@
         <v>238</v>
       </c>
       <c r="E114" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F114" t="s">
         <v>97</v>
@@ -10231,7 +10230,7 @@
         <v>354</v>
       </c>
       <c r="M114" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N114" t="s">
         <v>34</v>
@@ -10240,7 +10239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16">
       <c r="A115" s="2" t="s">
         <v>440</v>
       </c>
@@ -10276,7 +10275,7 @@
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>25</v>
@@ -10286,7 +10285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16">
       <c r="A116" t="s">
         <v>443</v>
       </c>
@@ -10303,10 +10302,10 @@
         <v>124</v>
       </c>
       <c r="F116" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G116" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -10330,7 +10329,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16">
       <c r="A117" s="2" t="s">
         <v>445</v>
       </c>
@@ -10378,7 +10377,7 @@
       </c>
       <c r="P117" s="2"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16">
       <c r="A118" t="s">
         <v>448</v>
       </c>
@@ -10392,7 +10391,7 @@
         <v>327</v>
       </c>
       <c r="E118" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F118" t="s">
         <v>83</v>
@@ -10422,7 +10421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16">
       <c r="A119" s="2" t="s">
         <v>451</v>
       </c>
@@ -10470,7 +10469,7 @@
       </c>
       <c r="P119" s="2"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16">
       <c r="A120" t="s">
         <v>453</v>
       </c>
@@ -10517,7 +10516,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16">
       <c r="A121" s="2" t="s">
         <v>457</v>
       </c>
@@ -10531,7 +10530,7 @@
         <v>178</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>157</v>
@@ -10565,7 +10564,7 @@
       </c>
       <c r="P121" s="2"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16">
       <c r="A122" t="s">
         <v>459</v>
       </c>
@@ -10579,7 +10578,7 @@
         <v>447</v>
       </c>
       <c r="E122" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F122" t="s">
         <v>169</v>
@@ -10612,7 +10611,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16">
       <c r="A123" s="2" t="s">
         <v>461</v>
       </c>
@@ -10660,7 +10659,7 @@
       </c>
       <c r="P123" s="2"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16">
       <c r="A124" t="s">
         <v>465</v>
       </c>
@@ -10674,7 +10673,7 @@
         <v>39</v>
       </c>
       <c r="E124" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F124" t="s">
         <v>389</v>
@@ -10707,7 +10706,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16">
       <c r="A125" s="2" t="s">
         <v>467</v>
       </c>
@@ -10755,7 +10754,7 @@
       </c>
       <c r="P125" s="2"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16">
       <c r="A126" t="s">
         <v>470</v>
       </c>
@@ -10802,7 +10801,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16">
       <c r="A127" s="2" t="s">
         <v>473</v>
       </c>
@@ -10850,7 +10849,7 @@
       </c>
       <c r="P127" s="2"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16">
       <c r="A128" t="s">
         <v>475</v>
       </c>
@@ -10864,7 +10863,7 @@
         <v>163</v>
       </c>
       <c r="E128" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F128" t="s">
         <v>243</v>
@@ -10897,7 +10896,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16">
       <c r="A129" s="2" t="s">
         <v>478</v>
       </c>
@@ -10945,7 +10944,7 @@
       </c>
       <c r="P129" s="2"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16">
       <c r="A130" t="s">
         <v>482</v>
       </c>
@@ -10956,10 +10955,10 @@
         <v>480</v>
       </c>
       <c r="D130" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E130" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F130" t="s">
         <v>389</v>
@@ -10992,7 +10991,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16">
       <c r="A131" s="2" t="s">
         <v>484</v>
       </c>
@@ -11036,7 +11035,7 @@
       <c r="O131" s="2"/>
       <c r="P131" s="2"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16">
       <c r="A132" t="s">
         <v>487</v>
       </c>
@@ -11050,7 +11049,7 @@
         <v>178</v>
       </c>
       <c r="E132" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F132" t="s">
         <v>68</v>
@@ -11083,7 +11082,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16">
       <c r="A133" s="2" t="s">
         <v>489</v>
       </c>
@@ -11131,7 +11130,7 @@
       </c>
       <c r="P133" s="2"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16">
       <c r="A134" t="s">
         <v>492</v>
       </c>
@@ -11178,7 +11177,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16">
       <c r="A135" s="2" t="s">
         <v>494</v>
       </c>
@@ -11192,7 +11191,7 @@
         <v>109</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>223</v>
@@ -11224,7 +11223,7 @@
       <c r="O135" s="2"/>
       <c r="P135" s="2"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16">
       <c r="A136" t="s">
         <v>496</v>
       </c>
@@ -11271,7 +11270,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16">
       <c r="A137" s="2" t="s">
         <v>500</v>
       </c>
@@ -11317,7 +11316,7 @@
       <c r="O137" s="2"/>
       <c r="P137" s="2"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16">
       <c r="A138" t="s">
         <v>502</v>
       </c>
@@ -11364,7 +11363,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16">
       <c r="A139" s="2" t="s">
         <v>505</v>
       </c>
@@ -11378,7 +11377,7 @@
         <v>82</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>21</v>
@@ -11410,7 +11409,7 @@
       <c r="O139" s="2"/>
       <c r="P139" s="2"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16">
       <c r="A140" t="s">
         <v>507</v>
       </c>
@@ -11451,7 +11450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16">
       <c r="A141" s="2" t="s">
         <v>510</v>
       </c>
@@ -11497,7 +11496,7 @@
       </c>
       <c r="P141" s="2"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16">
       <c r="A142" t="s">
         <v>512</v>
       </c>
@@ -11544,7 +11543,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16">
       <c r="A143" s="2" t="s">
         <v>514</v>
       </c>
@@ -11588,7 +11587,7 @@
       <c r="O143" s="2"/>
       <c r="P143" s="2"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16">
       <c r="A144" t="s">
         <v>516</v>
       </c>
@@ -11599,7 +11598,7 @@
         <v>518</v>
       </c>
       <c r="D144" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E144" t="s">
         <v>142</v>
@@ -11635,7 +11634,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16">
       <c r="A145" s="2" t="s">
         <v>519</v>
       </c>
@@ -11683,7 +11682,7 @@
       </c>
       <c r="P145" s="2"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16">
       <c r="A146" t="s">
         <v>521</v>
       </c>
@@ -11700,10 +11699,10 @@
         <v>142</v>
       </c>
       <c r="F146" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G146" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H146">
         <v>3</v>
@@ -11727,7 +11726,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16">
       <c r="A147" s="2" t="s">
         <v>523</v>
       </c>
@@ -11765,7 +11764,7 @@
         <v>211</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N147" s="2" t="s">
         <v>25</v>
@@ -11775,7 +11774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16">
       <c r="A148" t="s">
         <v>526</v>
       </c>
@@ -11822,7 +11821,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16">
       <c r="A149" s="2" t="s">
         <v>529</v>
       </c>
@@ -11839,10 +11838,10 @@
         <v>40</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2">
         <v>2</v>
@@ -11870,7 +11869,7 @@
       </c>
       <c r="P149" s="2"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16">
       <c r="A150" t="s">
         <v>533</v>
       </c>
@@ -11917,7 +11916,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16">
       <c r="A151" s="2" t="s">
         <v>535</v>
       </c>
@@ -11965,7 +11964,7 @@
       </c>
       <c r="P151" s="2"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16">
       <c r="A152" t="s">
         <v>537</v>
       </c>
@@ -12012,7 +12011,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16">
       <c r="A153" s="2" t="s">
         <v>540</v>
       </c>
@@ -12060,7 +12059,7 @@
       </c>
       <c r="P153" s="2"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16">
       <c r="A154" t="s">
         <v>542</v>
       </c>
@@ -12074,7 +12073,7 @@
         <v>348</v>
       </c>
       <c r="E154" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F154" t="s">
         <v>97</v>
@@ -12104,7 +12103,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16">
       <c r="A155" s="2" t="s">
         <v>544</v>
       </c>
@@ -12142,7 +12141,7 @@
         <v>253</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N155" s="2" t="s">
         <v>25</v>
@@ -12152,7 +12151,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16">
       <c r="A156" t="s">
         <v>546</v>
       </c>
@@ -12190,7 +12189,7 @@
         <v>393</v>
       </c>
       <c r="M156" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N156" t="s">
         <v>25</v>
@@ -12199,7 +12198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16">
       <c r="A157" s="2" t="s">
         <v>548</v>
       </c>
@@ -12245,7 +12244,7 @@
       </c>
       <c r="P157" s="2"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16">
       <c r="A158" t="s">
         <v>551</v>
       </c>
@@ -12289,7 +12288,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16">
       <c r="A159" s="2" t="s">
         <v>553</v>
       </c>
@@ -12337,7 +12336,7 @@
       </c>
       <c r="P159" s="2"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16">
       <c r="A160" t="s">
         <v>556</v>
       </c>
@@ -12384,7 +12383,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16">
       <c r="A161" s="2" t="s">
         <v>559</v>
       </c>
@@ -12422,7 +12421,7 @@
         <v>194</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N161" s="2" t="s">
         <v>25</v>
@@ -12432,7 +12431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16">
       <c r="A162" t="s">
         <v>562</v>
       </c>
@@ -12479,7 +12478,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16">
       <c r="A163" s="2" t="s">
         <v>565</v>
       </c>
@@ -12496,10 +12495,10 @@
         <v>20</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H163" s="2">
         <v>2</v>
@@ -12527,7 +12526,7 @@
       </c>
       <c r="P163" s="2"/>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16">
       <c r="A164" t="s">
         <v>569</v>
       </c>
@@ -12565,7 +12564,7 @@
         <v>564</v>
       </c>
       <c r="M164" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N164" t="s">
         <v>34</v>
@@ -12574,7 +12573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16">
       <c r="A165" s="2" t="s">
         <v>571</v>
       </c>
@@ -12620,7 +12619,7 @@
       <c r="O165" s="2"/>
       <c r="P165" s="2"/>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16">
       <c r="A166" t="s">
         <v>574</v>
       </c>
@@ -12634,7 +12633,7 @@
         <v>67</v>
       </c>
       <c r="E166" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F166" t="s">
         <v>223</v>
@@ -12655,7 +12654,7 @@
         <v>5</v>
       </c>
       <c r="M166" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N166" t="s">
         <v>25</v>
@@ -12664,7 +12663,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16">
       <c r="A167" s="2" t="s">
         <v>577</v>
       </c>
@@ -12710,7 +12709,7 @@
       <c r="O167" s="2"/>
       <c r="P167" s="2"/>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16">
       <c r="A168" t="s">
         <v>579</v>
       </c>
@@ -12754,7 +12753,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16">
       <c r="A169" s="2" t="s">
         <v>581</v>
       </c>
@@ -12792,7 +12791,7 @@
         <v>159</v>
       </c>
       <c r="M169" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N169" s="2" t="s">
         <v>25</v>
@@ -12802,7 +12801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16">
       <c r="A170" t="s">
         <v>583</v>
       </c>
@@ -12816,7 +12815,7 @@
         <v>168</v>
       </c>
       <c r="E170" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F170" t="s">
         <v>56</v>
@@ -12849,7 +12848,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16">
       <c r="A171" s="2" t="s">
         <v>586</v>
       </c>
@@ -12863,7 +12862,7 @@
         <v>109</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>61</v>
@@ -12897,7 +12896,7 @@
       </c>
       <c r="P171" s="2"/>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16">
       <c r="A172" t="s">
         <v>588</v>
       </c>
@@ -12944,7 +12943,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16">
       <c r="A173" s="2" t="s">
         <v>592</v>
       </c>
@@ -12958,7 +12957,7 @@
         <v>373</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>83</v>
@@ -12990,7 +12989,7 @@
       <c r="O173" s="2"/>
       <c r="P173" s="2"/>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16">
       <c r="A174" t="s">
         <v>594</v>
       </c>
@@ -13004,7 +13003,7 @@
         <v>217</v>
       </c>
       <c r="E174" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F174" t="s">
         <v>68</v>
@@ -13037,7 +13036,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16">
       <c r="A175" s="2" t="s">
         <v>596</v>
       </c>
@@ -13083,7 +13082,7 @@
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16">
       <c r="A176" t="s">
         <v>598</v>
       </c>
@@ -13127,7 +13126,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16">
       <c r="A177" s="2" t="s">
         <v>600</v>
       </c>
@@ -13141,7 +13140,7 @@
         <v>29</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>83</v>
@@ -13173,7 +13172,7 @@
       <c r="O177" s="2"/>
       <c r="P177" s="2"/>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16">
       <c r="A178" t="s">
         <v>602</v>
       </c>
@@ -13220,7 +13219,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16">
       <c r="A179" s="2" t="s">
         <v>605</v>
       </c>
@@ -13266,7 +13265,7 @@
       <c r="O179" s="2"/>
       <c r="P179" s="2"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16">
       <c r="A180" t="s">
         <v>609</v>
       </c>
@@ -13283,10 +13282,10 @@
         <v>40</v>
       </c>
       <c r="F180" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G180" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -13301,10 +13300,10 @@
         <v>0.2</v>
       </c>
       <c r="L180" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M180" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N180" t="s">
         <v>25</v>
@@ -13313,7 +13312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16">
       <c r="A181" s="2" t="s">
         <v>611</v>
       </c>
@@ -13327,7 +13326,7 @@
         <v>447</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>169</v>
@@ -13349,7 +13348,7 @@
       </c>
       <c r="L181" s="2"/>
       <c r="M181" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N181" s="2" t="s">
         <v>25</v>
@@ -13359,7 +13358,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16">
       <c r="A182" t="s">
         <v>613</v>
       </c>
@@ -13406,7 +13405,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16">
       <c r="A183" s="2" t="s">
         <v>618</v>
       </c>
@@ -13420,7 +13419,7 @@
         <v>404</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F183" s="2" t="s">
         <v>83</v>
@@ -13454,7 +13453,7 @@
       </c>
       <c r="P183" s="2"/>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16">
       <c r="A184" t="s">
         <v>622</v>
       </c>
@@ -13468,7 +13467,7 @@
         <v>153</v>
       </c>
       <c r="E184" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F184" t="s">
         <v>68</v>
@@ -13501,7 +13500,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16">
       <c r="A185" s="2" t="s">
         <v>625</v>
       </c>
@@ -13515,7 +13514,7 @@
         <v>312</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>41</v>
@@ -13539,7 +13538,7 @@
         <v>204</v>
       </c>
       <c r="M185" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N185" s="2" t="s">
         <v>52</v>
@@ -13549,7 +13548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16">
       <c r="A186" t="s">
         <v>627</v>
       </c>
@@ -13596,7 +13595,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16">
       <c r="A187" s="2" t="s">
         <v>629</v>
       </c>
@@ -13644,7 +13643,7 @@
       </c>
       <c r="P187" s="2"/>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16">
       <c r="A188" t="s">
         <v>631</v>
       </c>
@@ -13658,7 +13657,7 @@
         <v>447</v>
       </c>
       <c r="E188" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F188" t="s">
         <v>148</v>
@@ -13688,7 +13687,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16">
       <c r="A189" s="2" t="s">
         <v>634</v>
       </c>
@@ -13736,7 +13735,7 @@
       </c>
       <c r="P189" s="2"/>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16">
       <c r="A190" t="s">
         <v>638</v>
       </c>
@@ -13780,7 +13779,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16">
       <c r="A191" s="2" t="s">
         <v>640</v>
       </c>
@@ -13828,7 +13827,7 @@
       </c>
       <c r="P191" s="2"/>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16">
       <c r="A192" t="s">
         <v>643</v>
       </c>
@@ -13872,7 +13871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16">
       <c r="A193" s="2" t="s">
         <v>645</v>
       </c>
@@ -13910,7 +13909,7 @@
         <v>33</v>
       </c>
       <c r="M193" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N193" s="2" t="s">
         <v>25</v>
@@ -13920,7 +13919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16">
       <c r="A194" t="s">
         <v>647</v>
       </c>
@@ -13964,7 +13963,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16">
       <c r="A195" s="2" t="s">
         <v>649</v>
       </c>
@@ -14002,7 +14001,7 @@
         <v>262</v>
       </c>
       <c r="M195" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N195" s="2" t="s">
         <v>52</v>
@@ -14012,7 +14011,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16">
       <c r="A196" t="s">
         <v>652</v>
       </c>
@@ -14059,7 +14058,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16">
       <c r="A197" s="2" t="s">
         <v>655</v>
       </c>
@@ -14107,7 +14106,7 @@
       </c>
       <c r="P197" s="2"/>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16">
       <c r="A198" t="s">
         <v>658</v>
       </c>
@@ -14151,7 +14150,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16">
       <c r="A199" s="2" t="s">
         <v>660</v>
       </c>
@@ -14199,7 +14198,7 @@
       </c>
       <c r="P199" s="2"/>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16">
       <c r="A200" t="s">
         <v>663</v>
       </c>
@@ -14243,7 +14242,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16">
       <c r="A201" s="2" t="s">
         <v>666</v>
       </c>
@@ -14289,7 +14288,7 @@
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16">
       <c r="A202" t="s">
         <v>669</v>
       </c>
@@ -14336,7 +14335,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16">
       <c r="A203" s="2" t="s">
         <v>672</v>
       </c>
@@ -14384,7 +14383,7 @@
       </c>
       <c r="P203" s="2"/>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16">
       <c r="A204" t="s">
         <v>675</v>
       </c>
@@ -14428,7 +14427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16">
       <c r="A205" s="2" t="s">
         <v>677</v>
       </c>
@@ -14442,7 +14441,7 @@
         <v>104</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>68</v>
@@ -14476,7 +14475,7 @@
       </c>
       <c r="P205" s="2"/>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16">
       <c r="A206" t="s">
         <v>679</v>
       </c>
@@ -14487,7 +14486,7 @@
         <v>674</v>
       </c>
       <c r="D206" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E206" t="s">
         <v>154</v>
@@ -14523,7 +14522,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16">
       <c r="A207" s="2" t="s">
         <v>681</v>
       </c>
@@ -14561,7 +14560,7 @@
         <v>564</v>
       </c>
       <c r="M207" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N207" s="2" t="s">
         <v>25</v>
@@ -14571,7 +14570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16">
       <c r="A208" t="s">
         <v>683</v>
       </c>
@@ -14618,7 +14617,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16">
       <c r="A209" s="2" t="s">
         <v>686</v>
       </c>
@@ -14666,7 +14665,7 @@
       </c>
       <c r="P209" s="2"/>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16">
       <c r="A210" t="s">
         <v>688</v>
       </c>
@@ -14710,7 +14709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16">
       <c r="A211" s="2" t="s">
         <v>690</v>
       </c>
@@ -14758,7 +14757,7 @@
       </c>
       <c r="P211" s="2"/>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16">
       <c r="A212" t="s">
         <v>692</v>
       </c>
@@ -14805,7 +14804,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16">
       <c r="A213" s="2" t="s">
         <v>695</v>
       </c>
@@ -14853,7 +14852,7 @@
       </c>
       <c r="P213" s="2"/>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16">
       <c r="A214" t="s">
         <v>697</v>
       </c>
@@ -14897,7 +14896,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16">
       <c r="A215" s="2" t="s">
         <v>699</v>
       </c>
@@ -14911,7 +14910,7 @@
         <v>39</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>61</v>
@@ -14943,7 +14942,7 @@
       <c r="O215" s="2"/>
       <c r="P215" s="2"/>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16">
       <c r="A216" t="s">
         <v>702</v>
       </c>
@@ -14957,7 +14956,7 @@
         <v>447</v>
       </c>
       <c r="E216" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F216" t="s">
         <v>148</v>
@@ -14990,7 +14989,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16">
       <c r="A217" s="2" t="s">
         <v>704</v>
       </c>
@@ -15004,7 +15003,7 @@
         <v>121</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>61</v>
@@ -15038,7 +15037,7 @@
       </c>
       <c r="P217" s="2"/>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16">
       <c r="A218" t="s">
         <v>707</v>
       </c>
@@ -15085,7 +15084,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16">
       <c r="A219" s="2" t="s">
         <v>709</v>
       </c>
@@ -15133,7 +15132,7 @@
       </c>
       <c r="P219" s="2"/>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16">
       <c r="A220" t="s">
         <v>713</v>
       </c>
@@ -15147,13 +15146,13 @@
         <v>39</v>
       </c>
       <c r="E220" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F220" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G220" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H220">
         <v>2</v>
@@ -15177,7 +15176,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16">
       <c r="A221" s="2" t="s">
         <v>716</v>
       </c>
@@ -15223,7 +15222,7 @@
       <c r="O221" s="2"/>
       <c r="P221" s="2"/>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16">
       <c r="A222" t="s">
         <v>718</v>
       </c>
@@ -15237,7 +15236,7 @@
         <v>235</v>
       </c>
       <c r="E222" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F222" t="s">
         <v>389</v>
@@ -15270,7 +15269,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16">
       <c r="A223" s="2" t="s">
         <v>720</v>
       </c>
@@ -15316,7 +15315,7 @@
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16">
       <c r="A224" t="s">
         <v>722</v>
       </c>
@@ -15363,7 +15362,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16">
       <c r="A225" s="2" t="s">
         <v>724</v>
       </c>
@@ -15374,7 +15373,7 @@
         <v>726</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>40</v>
@@ -15409,7 +15408,7 @@
       <c r="O225" s="2"/>
       <c r="P225" s="2"/>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16">
       <c r="A226" t="s">
         <v>727</v>
       </c>
@@ -15456,7 +15455,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16">
       <c r="A227" s="2" t="s">
         <v>729</v>
       </c>
@@ -15470,7 +15469,7 @@
         <v>147</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>41</v>
@@ -15504,7 +15503,7 @@
       </c>
       <c r="P227" s="2"/>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16">
       <c r="A228" t="s">
         <v>732</v>
       </c>
@@ -15548,7 +15547,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16">
       <c r="A229" s="2" t="s">
         <v>734</v>
       </c>
@@ -15562,7 +15561,7 @@
         <v>235</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>56</v>
@@ -15594,7 +15593,7 @@
       <c r="O229" s="2"/>
       <c r="P229" s="2"/>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16">
       <c r="A230" t="s">
         <v>737</v>
       </c>
@@ -15641,7 +15640,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16">
       <c r="A231" s="2" t="s">
         <v>740</v>
       </c>
@@ -15679,7 +15678,7 @@
         <v>239</v>
       </c>
       <c r="M231" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N231" s="2" t="s">
         <v>34</v>
@@ -15689,7 +15688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16">
       <c r="A232" t="s">
         <v>742</v>
       </c>
@@ -15733,7 +15732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16">
       <c r="A233" s="2" t="s">
         <v>744</v>
       </c>
@@ -15779,7 +15778,7 @@
       <c r="O233" s="2"/>
       <c r="P233" s="2"/>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16">
       <c r="A234" t="s">
         <v>746</v>
       </c>
@@ -15823,7 +15822,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16">
       <c r="A235" s="2" t="s">
         <v>749</v>
       </c>
@@ -15871,7 +15870,7 @@
       </c>
       <c r="P235" s="2"/>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16">
       <c r="A236" t="s">
         <v>752</v>
       </c>
@@ -15885,7 +15884,7 @@
         <v>104</v>
       </c>
       <c r="E236" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F236" t="s">
         <v>243</v>
@@ -15918,7 +15917,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16">
       <c r="A237" s="2" t="s">
         <v>754</v>
       </c>
@@ -15932,7 +15931,7 @@
         <v>348</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F237" s="2" t="s">
         <v>90</v>
@@ -15962,7 +15961,7 @@
       <c r="O237" s="2"/>
       <c r="P237" s="2"/>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16">
       <c r="A238" t="s">
         <v>757</v>
       </c>
@@ -16006,7 +16005,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16">
       <c r="A239" s="2" t="s">
         <v>759</v>
       </c>
@@ -16054,7 +16053,7 @@
       </c>
       <c r="P239" s="2"/>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16">
       <c r="A240" t="s">
         <v>762</v>
       </c>
@@ -16098,7 +16097,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16">
       <c r="A241" s="2" t="s">
         <v>765</v>
       </c>
@@ -16144,7 +16143,7 @@
       <c r="O241" s="2"/>
       <c r="P241" s="2"/>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16">
       <c r="A242" t="s">
         <v>768</v>
       </c>
@@ -16158,7 +16157,7 @@
         <v>147</v>
       </c>
       <c r="E242" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F242" t="s">
         <v>157</v>
@@ -16191,7 +16190,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16">
       <c r="A243" s="2" t="s">
         <v>770</v>
       </c>
@@ -16229,7 +16228,7 @@
         <v>231</v>
       </c>
       <c r="M243" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N243" s="2" t="s">
         <v>25</v>
@@ -16239,7 +16238,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16">
       <c r="A244" t="s">
         <v>772</v>
       </c>
@@ -16286,7 +16285,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16">
       <c r="A245" s="2" t="s">
         <v>775</v>
       </c>
@@ -16334,7 +16333,7 @@
       </c>
       <c r="P245" s="2"/>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16">
       <c r="A246" t="s">
         <v>777</v>
       </c>
@@ -16381,7 +16380,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16">
       <c r="A247" s="2" t="s">
         <v>779</v>
       </c>
@@ -16429,7 +16428,7 @@
       </c>
       <c r="P247" s="2"/>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16">
       <c r="A248" t="s">
         <v>781</v>
       </c>
@@ -16476,7 +16475,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16">
       <c r="A249" s="2" t="s">
         <v>784</v>
       </c>
@@ -16524,7 +16523,7 @@
       </c>
       <c r="P249" s="2"/>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16">
       <c r="A250" t="s">
         <v>787</v>
       </c>
@@ -16562,7 +16561,7 @@
         <v>281</v>
       </c>
       <c r="M250" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N250" t="s">
         <v>25</v>
@@ -16571,7 +16570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16">
       <c r="A251" s="2" t="s">
         <v>789</v>
       </c>
@@ -16619,7 +16618,7 @@
       </c>
       <c r="P251" s="2"/>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16">
       <c r="A252" t="s">
         <v>792</v>
       </c>
@@ -16630,7 +16629,7 @@
         <v>794</v>
       </c>
       <c r="D252" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E252" t="s">
         <v>142</v>
@@ -16663,7 +16662,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16">
       <c r="A253" s="2" t="s">
         <v>795</v>
       </c>
@@ -16677,7 +16676,7 @@
         <v>404</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>169</v>
@@ -16709,7 +16708,7 @@
       <c r="O253" s="2"/>
       <c r="P253" s="2"/>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16">
       <c r="A254" t="s">
         <v>798</v>
       </c>
@@ -16747,7 +16746,7 @@
         <v>70</v>
       </c>
       <c r="M254" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N254" t="s">
         <v>25</v>
@@ -16756,7 +16755,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16">
       <c r="A255" s="2" t="s">
         <v>801</v>
       </c>
@@ -16802,7 +16801,7 @@
       <c r="O255" s="2"/>
       <c r="P255" s="2"/>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16">
       <c r="A256" t="s">
         <v>804</v>
       </c>
@@ -16849,7 +16848,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16">
       <c r="A257" s="2" t="s">
         <v>808</v>
       </c>
@@ -16897,7 +16896,7 @@
       </c>
       <c r="P257" s="2"/>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16">
       <c r="A258" t="s">
         <v>811</v>
       </c>
@@ -16944,7 +16943,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16">
       <c r="A259" s="2" t="s">
         <v>815</v>
       </c>
@@ -16992,7 +16991,7 @@
       </c>
       <c r="P259" s="2"/>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16">
       <c r="A260" t="s">
         <v>817</v>
       </c>
@@ -17039,7 +17038,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16">
       <c r="A261" s="2" t="s">
         <v>819</v>
       </c>
@@ -17077,7 +17076,7 @@
         <v>822</v>
       </c>
       <c r="M261" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N261" s="2" t="s">
         <v>25</v>
@@ -17087,7 +17086,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16">
       <c r="A262" t="s">
         <v>823</v>
       </c>
@@ -17125,7 +17124,7 @@
         <v>591</v>
       </c>
       <c r="M262" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N262" t="s">
         <v>25</v>
@@ -17134,7 +17133,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:16">
       <c r="A263" s="2" t="s">
         <v>825</v>
       </c>
@@ -17148,7 +17147,7 @@
         <v>75</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>83</v>
@@ -17180,7 +17179,7 @@
       </c>
       <c r="P263" s="2"/>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16">
       <c r="A264" t="s">
         <v>828</v>
       </c>
@@ -17227,7 +17226,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16">
       <c r="A265" s="2" t="s">
         <v>831</v>
       </c>
@@ -17275,7 +17274,7 @@
       </c>
       <c r="P265" s="2"/>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16">
       <c r="A266" t="s">
         <v>833</v>
       </c>
@@ -17289,7 +17288,7 @@
         <v>217</v>
       </c>
       <c r="E266" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F266" t="s">
         <v>223</v>
@@ -17322,7 +17321,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16">
       <c r="A267" s="2" t="s">
         <v>835</v>
       </c>
@@ -17370,7 +17369,7 @@
       </c>
       <c r="P267" s="2"/>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16">
       <c r="A268" t="s">
         <v>837</v>
       </c>
@@ -17414,7 +17413,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16">
       <c r="A269" s="2" t="s">
         <v>841</v>
       </c>
@@ -17462,7 +17461,7 @@
       </c>
       <c r="P269" s="2"/>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16">
       <c r="A270" t="s">
         <v>843</v>
       </c>
@@ -17509,7 +17508,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16">
       <c r="A271" s="2" t="s">
         <v>846</v>
       </c>
@@ -17557,7 +17556,7 @@
       </c>
       <c r="P271" s="2"/>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16">
       <c r="A272" t="s">
         <v>849</v>
       </c>
@@ -17604,7 +17603,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16">
       <c r="A273" s="2" t="s">
         <v>851</v>
       </c>
@@ -17618,7 +17617,7 @@
         <v>174</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>115</v>
@@ -17652,7 +17651,7 @@
       </c>
       <c r="P273" s="2"/>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16">
       <c r="A274" t="s">
         <v>854</v>
       </c>
@@ -17696,7 +17695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16">
       <c r="A275" s="2" t="s">
         <v>856</v>
       </c>
@@ -17713,10 +17712,10 @@
         <v>30</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H275" s="2">
         <v>2</v>
@@ -17734,7 +17733,7 @@
         <v>532</v>
       </c>
       <c r="M275" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N275" s="2" t="s">
         <v>25</v>
@@ -17744,7 +17743,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16">
       <c r="A276" t="s">
         <v>859</v>
       </c>
@@ -17782,7 +17781,7 @@
         <v>407</v>
       </c>
       <c r="M276" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N276" t="s">
         <v>25</v>
@@ -17791,7 +17790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16">
       <c r="A277" s="2" t="s">
         <v>861</v>
       </c>
@@ -17837,7 +17836,7 @@
       <c r="O277" s="2"/>
       <c r="P277" s="2"/>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16">
       <c r="A278" t="s">
         <v>864</v>
       </c>
@@ -17881,7 +17880,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16">
       <c r="A279" s="2" t="s">
         <v>866</v>
       </c>
@@ -17895,7 +17894,7 @@
         <v>238</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F279" s="2" t="s">
         <v>56</v>
@@ -17919,7 +17918,7 @@
         <v>58</v>
       </c>
       <c r="M279" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N279" s="2" t="s">
         <v>25</v>
@@ -17929,7 +17928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16">
       <c r="A280" t="s">
         <v>868</v>
       </c>
@@ -17976,7 +17975,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16">
       <c r="A281" s="2" t="s">
         <v>870</v>
       </c>
@@ -17990,7 +17989,7 @@
         <v>428</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>179</v>
@@ -18020,7 +18019,7 @@
       <c r="O281" s="2"/>
       <c r="P281" s="2"/>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16">
       <c r="A282" t="s">
         <v>873</v>
       </c>
@@ -18034,7 +18033,7 @@
         <v>433</v>
       </c>
       <c r="E282" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F282" t="s">
         <v>21</v>
@@ -18058,7 +18057,7 @@
         <v>132</v>
       </c>
       <c r="M282" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N282" t="s">
         <v>52</v>
@@ -18067,7 +18066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16">
       <c r="A283" s="2" t="s">
         <v>876</v>
       </c>
@@ -18113,7 +18112,7 @@
       <c r="O283" s="2"/>
       <c r="P283" s="2"/>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16">
       <c r="A284" t="s">
         <v>878</v>
       </c>
@@ -18127,7 +18126,7 @@
         <v>141</v>
       </c>
       <c r="E284" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F284" t="s">
         <v>389</v>
@@ -18160,34 +18159,39 @@
         <v>875</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16">
       <c r="M285" s="2"/>
       <c r="N285" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P284" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P284"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="true" style="0"/>
+    <col min="2" max="2" width="21.140625" customWidth="true" style="0"/>
+    <col min="3" max="3" width="22.28515625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="25.85546875" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.28515625" customWidth="true" style="0"/>
+    <col min="6" max="6" width="20" customWidth="true" style="0"/>
+    <col min="7" max="7" width="23.42578125" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.5703125" customWidth="true" style="0"/>
+    <col min="9" max="9" width="12.85546875" customWidth="true" style="0"/>
+    <col min="10" max="10" width="22.28515625" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" customHeight="1" ht="21.95">
       <c r="A1" s="3" t="s">
         <v>1129</v>
       </c>
@@ -18219,7 +18223,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1245</v>
       </c>
@@ -18251,7 +18255,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>1223</v>
       </c>
@@ -18283,7 +18287,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>1202</v>
       </c>
@@ -18315,7 +18319,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>1178</v>
       </c>
@@ -18347,7 +18351,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>1136</v>
       </c>
@@ -18377,23 +18381,28 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
+  <autoFilter ref="A1:J1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="25.85546875" customWidth="true" style="0"/>
+    <col min="3" max="3" width="35.28515625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16.42578125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" customHeight="1" ht="21.95">
       <c r="A1" s="8" t="s">
         <v>1130</v>
       </c>
@@ -18407,7 +18416,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>1407</v>
       </c>
@@ -18421,7 +18430,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>1407</v>
       </c>
@@ -18435,7 +18444,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>1407</v>
       </c>
@@ -18449,7 +18458,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>1407</v>
       </c>
@@ -18463,7 +18472,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>1407</v>
       </c>
@@ -18477,7 +18486,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>1407</v>
       </c>
@@ -18491,7 +18500,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>1407</v>
       </c>
@@ -18505,7 +18514,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>1423</v>
       </c>
@@ -18519,7 +18528,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>1423</v>
       </c>
@@ -18533,7 +18542,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>1423</v>
       </c>
@@ -18547,7 +18556,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>1423</v>
       </c>
@@ -18561,7 +18570,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>1423</v>
       </c>
@@ -18575,7 +18584,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>1434</v>
       </c>
@@ -18589,7 +18598,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>1434</v>
       </c>
@@ -18603,7 +18612,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>1434</v>
       </c>
@@ -18618,24 +18627,29 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
+  <autoFilter ref="A1:D1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.85546875" customWidth="true" style="0"/>
+    <col min="3" max="3" width="16.42578125" customWidth="true" style="0"/>
+    <col min="4" max="4" width="11.7109375" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16.42578125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" customHeight="1" ht="21.95">
       <c r="A1" s="6" t="s">
         <v>1442</v>
       </c>
@@ -18652,7 +18666,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>1446</v>
       </c>
@@ -18666,7 +18680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>1446</v>
       </c>
@@ -18683,7 +18697,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>1446</v>
       </c>
@@ -18691,7 +18705,7 @@
         <v>1245</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -18700,7 +18714,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>1446</v>
       </c>
@@ -18715,7 +18729,7 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>1446</v>
       </c>
@@ -18732,7 +18746,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>1446</v>
       </c>
@@ -18740,7 +18754,7 @@
         <v>1223</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D7" s="2">
         <v>8</v>
@@ -18749,7 +18763,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>1446</v>
       </c>
@@ -18763,7 +18777,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
         <v>1446</v>
       </c>
@@ -18780,7 +18794,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>1446</v>
       </c>
@@ -18788,7 +18802,7 @@
         <v>1202</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -18797,7 +18811,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>1446</v>
       </c>
@@ -18812,7 +18826,7 @@
       </c>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>1446</v>
       </c>
@@ -18829,7 +18843,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>1446</v>
       </c>
@@ -18837,7 +18851,7 @@
         <v>1178</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2">
         <v>10</v>
@@ -18846,7 +18860,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>1446</v>
       </c>
@@ -18860,7 +18874,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
         <v>1446</v>
       </c>
@@ -18877,7 +18891,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>1446</v>
       </c>
@@ -18885,7 +18899,7 @@
         <v>1136</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D16">
         <v>7</v>
@@ -18894,7 +18908,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>1457</v>
       </c>
@@ -18905,13 +18919,13 @@
         <v>1459</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>1460</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>1457</v>
       </c>
@@ -18928,7 +18942,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>1457</v>
       </c>
@@ -18945,7 +18959,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>1465</v>
       </c>
@@ -18962,7 +18976,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
         <v>1465</v>
       </c>
@@ -18979,7 +18993,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>1465</v>
       </c>
@@ -18997,33 +19011,38 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
+  <autoFilter ref="A1:E1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="18.7109375" customWidth="true" style="0"/>
+    <col min="3" max="3" width="16.42578125" customWidth="true" style="0"/>
+    <col min="4" max="4" width="18.7109375" customWidth="true" style="0"/>
+    <col min="5" max="5" width="12.85546875" customWidth="true" style="0"/>
+    <col min="6" max="6" width="36.42578125" customWidth="true" style="0"/>
+    <col min="7" max="7" width="28.140625" customWidth="true" style="0"/>
+    <col min="8" max="8" width="18.7109375" customWidth="true" style="0"/>
+    <col min="9" max="9" width="22.28515625" customWidth="true" style="0"/>
+    <col min="10" max="10" width="21.140625" customWidth="true" style="0"/>
+    <col min="11" max="11" width="16.42578125" customWidth="true" style="0"/>
+    <col min="12" max="12" width="21.140625" customWidth="true" style="0"/>
+    <col min="13" max="13" width="17.5703125" customWidth="true" style="0"/>
+    <col min="14" max="14" width="14" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" customHeight="1" ht="21.95">
       <c r="A1" s="3" t="s">
         <v>881</v>
       </c>
@@ -19067,24 +19086,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>888</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
         <v>889</v>
@@ -19111,7 +19130,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>894</v>
       </c>
@@ -19155,7 +19174,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>898</v>
       </c>
@@ -19169,7 +19188,7 @@
         <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
         <v>157</v>
@@ -19199,7 +19218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14">
       <c r="A5" s="2" t="s">
         <v>899</v>
       </c>
@@ -19213,7 +19232,7 @@
         <v>168</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>169</v>
@@ -19243,7 +19262,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>904</v>
       </c>
@@ -19287,7 +19306,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
         <v>906</v>
       </c>
@@ -19298,7 +19317,7 @@
         <v>203</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>40</v>
@@ -19331,7 +19350,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>908</v>
       </c>
@@ -19345,7 +19364,7 @@
         <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
         <v>76</v>
@@ -19375,7 +19394,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14">
       <c r="A9" s="2" t="s">
         <v>910</v>
       </c>
@@ -19389,7 +19408,7 @@
         <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>90</v>
@@ -19419,7 +19438,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>912</v>
       </c>
@@ -19463,7 +19482,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
         <v>913</v>
       </c>
@@ -19507,7 +19526,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>915</v>
       </c>
@@ -19551,7 +19570,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14">
       <c r="A13" s="2" t="s">
         <v>916</v>
       </c>
@@ -19595,7 +19614,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>918</v>
       </c>
@@ -19609,7 +19628,7 @@
         <v>238</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
         <v>97</v>
@@ -19639,7 +19658,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14">
       <c r="A15" s="2" t="s">
         <v>920</v>
       </c>
@@ -19683,7 +19702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>921</v>
       </c>
@@ -19727,7 +19746,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14">
       <c r="A17" s="2" t="s">
         <v>924</v>
       </c>
@@ -19771,7 +19790,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>926</v>
       </c>
@@ -19815,7 +19834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14">
       <c r="A19" s="2" t="s">
         <v>928</v>
       </c>
@@ -19859,7 +19878,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>929</v>
       </c>
@@ -19903,7 +19922,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14">
       <c r="A21" s="2" t="s">
         <v>931</v>
       </c>
@@ -19917,7 +19936,7 @@
         <v>67</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>223</v>
@@ -19947,7 +19966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>932</v>
       </c>
@@ -19991,7 +20010,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14">
       <c r="A23" s="2" t="s">
         <v>933</v>
       </c>
@@ -20008,7 +20027,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>900</v>
@@ -20035,7 +20054,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>934</v>
       </c>
@@ -20049,7 +20068,7 @@
         <v>447</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F24" t="s">
         <v>169</v>
@@ -20079,7 +20098,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14">
       <c r="A25" s="2" t="s">
         <v>935</v>
       </c>
@@ -20093,7 +20112,7 @@
         <v>312</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>41</v>
@@ -20123,7 +20142,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>936</v>
       </c>
@@ -20167,7 +20186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14">
       <c r="A27" s="2" t="s">
         <v>938</v>
       </c>
@@ -20211,7 +20230,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>941</v>
       </c>
@@ -20255,7 +20274,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14">
       <c r="A29" s="2" t="s">
         <v>942</v>
       </c>
@@ -20299,7 +20318,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>944</v>
       </c>
@@ -20343,7 +20362,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14">
       <c r="A31" s="2" t="s">
         <v>946</v>
       </c>
@@ -20387,7 +20406,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>949</v>
       </c>
@@ -20431,7 +20450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14">
       <c r="A33" s="2" t="s">
         <v>951</v>
       </c>
@@ -20475,7 +20494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>954</v>
       </c>
@@ -20519,7 +20538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14">
       <c r="A35" s="2" t="s">
         <v>955</v>
       </c>
@@ -20536,7 +20555,7 @@
         <v>30</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>900</v>
@@ -20563,7 +20582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>957</v>
       </c>
@@ -20607,7 +20626,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14">
       <c r="A37" s="2" t="s">
         <v>959</v>
       </c>
@@ -20621,7 +20640,7 @@
         <v>238</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>56</v>
@@ -20651,7 +20670,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
         <v>960</v>
       </c>
@@ -20665,7 +20684,7 @@
         <v>433</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -20696,28 +20715,34 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:N1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.85546875" customWidth="true" style="0"/>
+    <col min="3" max="3" width="14" customWidth="true" style="0"/>
+    <col min="4" max="4" width="22.28515625" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16.42578125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="21.140625" customWidth="true" style="0"/>
+    <col min="7" max="7" width="23.42578125" customWidth="true" style="0"/>
+    <col min="8" max="8" width="15.28515625" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.28515625" customWidth="true" style="0"/>
+    <col min="10" max="10" width="33" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" customHeight="1" ht="21.95">
       <c r="A1" s="4" t="s">
         <v>962</v>
       </c>
@@ -20749,7 +20774,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>969</v>
       </c>
@@ -20781,7 +20806,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>976</v>
       </c>
@@ -20813,7 +20838,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>981</v>
       </c>
@@ -20845,7 +20870,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>986</v>
       </c>
@@ -20875,7 +20900,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>992</v>
       </c>
@@ -20908,25 +20933,33 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:J1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.85546875" customWidth="true" style="0"/>
+    <col min="3" max="3" width="14" customWidth="true" style="0"/>
+    <col min="4" max="4" width="23.42578125" customWidth="true" style="0"/>
+    <col min="5" max="5" width="23.42578125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="22.28515625" customWidth="true" style="0"/>
+    <col min="7" max="7" width="22.28515625" customWidth="true" style="0"/>
+    <col min="8" max="8" width="23.42578125" customWidth="true" style="0"/>
+    <col min="9" max="9" width="23.42578125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" customHeight="1" ht="21.95">
       <c r="A1" s="5" t="s">
         <v>997</v>
       </c>
@@ -20955,7 +20988,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1003</v>
       </c>
@@ -20984,7 +21017,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>1008</v>
       </c>
@@ -21013,7 +21046,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>1012</v>
       </c>
@@ -21042,7 +21075,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>1016</v>
       </c>
@@ -21071,7 +21104,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>1020</v>
       </c>
@@ -21100,7 +21133,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>1024</v>
       </c>
@@ -21129,7 +21162,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>1028</v>
       </c>
@@ -21158,7 +21191,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>1032</v>
       </c>
@@ -21187,7 +21220,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>1036</v>
       </c>
@@ -21216,7 +21249,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>1040</v>
       </c>
@@ -21245,7 +21278,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>1044</v>
       </c>
@@ -21274,7 +21307,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>1048</v>
       </c>
@@ -21303,7 +21336,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>1052</v>
       </c>
@@ -21332,7 +21365,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>1056</v>
       </c>
@@ -21361,7 +21394,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>1060</v>
       </c>
@@ -21390,7 +21423,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>1064</v>
       </c>
@@ -21419,7 +21452,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>1068</v>
       </c>
@@ -21448,7 +21481,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>1072</v>
       </c>
@@ -21477,7 +21510,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>1076</v>
       </c>
@@ -21503,7 +21536,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>1080</v>
       </c>
@@ -21530,7 +21563,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>1082</v>
       </c>
@@ -21557,29 +21590,34 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:I1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="18.7109375" customWidth="true" style="0"/>
+    <col min="3" max="3" width="17.5703125" customWidth="true" style="0"/>
+    <col min="4" max="4" width="14" customWidth="true" style="0"/>
+    <col min="5" max="5" width="23.42578125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="71.85546875" customWidth="true" style="0"/>
+    <col min="7" max="7" width="23.42578125" customWidth="true" style="0"/>
+    <col min="8" max="8" width="12.85546875" customWidth="true" style="0"/>
+    <col min="9" max="9" width="23.42578125" customWidth="true" style="0"/>
+    <col min="10" max="10" width="44.7109375" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" customHeight="1" ht="21.95">
       <c r="A1" s="6" t="s">
         <v>1085</v>
       </c>
@@ -21611,7 +21649,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1092</v>
       </c>
@@ -21640,7 +21678,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>1099</v>
       </c>
@@ -21670,7 +21708,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>1103</v>
       </c>
@@ -21702,7 +21740,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>1108</v>
       </c>
@@ -21732,7 +21770,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>1111</v>
       </c>
@@ -21761,7 +21799,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
         <v>1114</v>
       </c>
@@ -21791,7 +21829,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>1118</v>
       </c>
@@ -21820,7 +21858,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
         <v>1121</v>
       </c>
@@ -21852,7 +21890,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>1124</v>
       </c>
@@ -21884,7 +21922,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
         <v>1126</v>
       </c>
@@ -21917,28 +21955,34 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:J1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:J43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="12.85546875" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true" style="0"/>
+    <col min="4" max="4" width="15.28515625" customWidth="true" style="0"/>
+    <col min="5" max="5" width="37.7109375" customWidth="true" style="0"/>
+    <col min="6" max="6" width="14" customWidth="true" style="0"/>
+    <col min="7" max="7" width="20" customWidth="true" style="0"/>
+    <col min="8" max="8" width="22.28515625" customWidth="true" style="0"/>
+    <col min="9" max="9" width="22.28515625" customWidth="true" style="0"/>
+    <col min="10" max="10" width="12.85546875" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" customHeight="1" ht="21.95">
       <c r="A1" s="7" t="s">
         <v>1128</v>
       </c>
@@ -21970,7 +22014,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1135</v>
       </c>
@@ -22002,7 +22046,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>1143</v>
       </c>
@@ -22034,7 +22078,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>1148</v>
       </c>
@@ -22066,7 +22110,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>1153</v>
       </c>
@@ -22098,7 +22142,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>1158</v>
       </c>
@@ -22130,7 +22174,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
         <v>1162</v>
       </c>
@@ -22162,7 +22206,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>1167</v>
       </c>
@@ -22194,7 +22238,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
         <v>1173</v>
       </c>
@@ -22226,7 +22270,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>1177</v>
       </c>
@@ -22258,7 +22302,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
         <v>1179</v>
       </c>
@@ -22290,7 +22334,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>1183</v>
       </c>
@@ -22322,7 +22366,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
         <v>1185</v>
       </c>
@@ -22354,7 +22398,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>1188</v>
       </c>
@@ -22386,7 +22430,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
         <v>1191</v>
       </c>
@@ -22418,7 +22462,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>1193</v>
       </c>
@@ -22450,7 +22494,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
         <v>1196</v>
       </c>
@@ -22482,7 +22526,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>1199</v>
       </c>
@@ -22514,7 +22558,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
         <v>1201</v>
       </c>
@@ -22546,7 +22590,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>1204</v>
       </c>
@@ -22578,7 +22622,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
         <v>1206</v>
       </c>
@@ -22610,7 +22654,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>1208</v>
       </c>
@@ -22642,7 +22686,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
         <v>1211</v>
       </c>
@@ -22674,7 +22718,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>1213</v>
       </c>
@@ -22706,7 +22750,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
         <v>1215</v>
       </c>
@@ -22738,7 +22782,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>1218</v>
       </c>
@@ -22770,7 +22814,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
         <v>1221</v>
       </c>
@@ -22802,7 +22846,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>1222</v>
       </c>
@@ -22834,7 +22878,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
         <v>1226</v>
       </c>
@@ -22866,7 +22910,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>1230</v>
       </c>
@@ -22898,7 +22942,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
         <v>1233</v>
       </c>
@@ -22930,7 +22974,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>1235</v>
       </c>
@@ -22962,7 +23006,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
         <v>1238</v>
       </c>
@@ -22994,7 +23038,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>1241</v>
       </c>
@@ -23026,7 +23070,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
         <v>1243</v>
       </c>
@@ -23058,7 +23102,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>1244</v>
       </c>
@@ -23090,7 +23134,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
         <v>1247</v>
       </c>
@@ -23122,7 +23166,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>1249</v>
       </c>
@@ -23154,7 +23198,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="A39" s="2" t="s">
         <v>1251</v>
       </c>
@@ -23186,7 +23230,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>1253</v>
       </c>
@@ -23218,7 +23262,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10">
       <c r="A41" s="2" t="s">
         <v>1256</v>
       </c>
@@ -23250,7 +23294,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>1257</v>
       </c>
@@ -23282,7 +23326,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
         <v>1258</v>
       </c>
@@ -23315,30 +23359,37 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A1:J1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:M21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="true" style="0"/>
+    <col min="2" max="2" width="9.28515625" customWidth="true" style="0"/>
+    <col min="3" max="3" width="36.42578125" customWidth="true" style="0"/>
+    <col min="4" max="4" width="17.5703125" customWidth="true" style="0"/>
+    <col min="5" max="5" width="17.5703125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="17.5703125" customWidth="true" style="0"/>
+    <col min="7" max="7" width="15.28515625" customWidth="true" style="0"/>
+    <col min="8" max="8" width="16.42578125" customWidth="true" style="0"/>
+    <col min="9" max="9" width="21.140625" customWidth="true" style="0"/>
+    <col min="10" max="10" width="20" customWidth="true" style="0"/>
+    <col min="11" max="11" width="18.7109375" customWidth="true" style="0"/>
+    <col min="12" max="12" width="16.42578125" customWidth="true" style="0"/>
+    <col min="13" max="13" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" customHeight="1" ht="21.95">
       <c r="A1" s="5" t="s">
         <v>1260</v>
       </c>
@@ -23379,7 +23430,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -23420,7 +23471,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -23461,21 +23512,21 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" t="s">
-        <v>48</v>
       </c>
       <c r="D4" t="s">
         <v>1278</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
         <v>958</v>
@@ -23502,7 +23553,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
         <v>126</v>
       </c>
@@ -23543,7 +23594,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>170</v>
       </c>
@@ -23584,7 +23635,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
         <v>149</v>
       </c>
@@ -23625,7 +23676,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -23666,7 +23717,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
         <v>98</v>
       </c>
@@ -23707,7 +23758,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -23724,7 +23775,7 @@
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
         <v>1289</v>
@@ -23748,7 +23799,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
         <v>77</v>
       </c>
@@ -23789,7 +23840,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>390</v>
       </c>
@@ -23830,7 +23881,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="A13" s="2" t="s">
         <v>244</v>
       </c>
@@ -23871,7 +23922,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -23912,7 +23963,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13">
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
@@ -23953,7 +24004,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -23994,7 +24045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13">
       <c r="A17" s="2" t="s">
         <v>180</v>
       </c>
@@ -24035,7 +24086,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -24076,7 +24127,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13">
       <c r="A19" s="2" t="s">
         <v>158</v>
       </c>
@@ -24117,7 +24168,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -24158,7 +24209,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
         <v>224</v>
       </c>
@@ -24200,29 +24251,34 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:M1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="true" style="0"/>
+    <col min="2" max="2" width="20" customWidth="true" style="0"/>
+    <col min="3" max="3" width="21.140625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="24.7109375" customWidth="true" style="0"/>
+    <col min="5" max="5" width="23.42578125" customWidth="true" style="0"/>
+    <col min="6" max="6" width="18.7109375" customWidth="true" style="0"/>
+    <col min="7" max="7" width="21.140625" customWidth="true" style="0"/>
+    <col min="8" max="8" width="20" customWidth="true" style="0"/>
+    <col min="9" max="9" width="22.28515625" customWidth="true" style="0"/>
+    <col min="10" max="10" width="17.5703125" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" customHeight="1" ht="21.95">
       <c r="A1" s="7" t="s">
         <v>1129</v>
       </c>
@@ -24254,7 +24310,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1136</v>
       </c>
@@ -24286,7 +24342,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>1178</v>
       </c>
@@ -24318,7 +24374,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>1202</v>
       </c>
@@ -24350,7 +24406,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>1223</v>
       </c>
@@ -24382,7 +24438,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>1245</v>
       </c>
@@ -24415,30 +24471,36 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:J1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="true" style="0"/>
+    <col min="2" max="2" width="21.140625" customWidth="true" style="0"/>
+    <col min="3" max="3" width="21.140625" customWidth="true" style="0"/>
+    <col min="4" max="4" width="20" customWidth="true" style="0"/>
+    <col min="5" max="5" width="22.28515625" customWidth="true" style="0"/>
+    <col min="6" max="6" width="20" customWidth="true" style="0"/>
+    <col min="7" max="7" width="23.42578125" customWidth="true" style="0"/>
+    <col min="8" max="8" width="22.28515625" customWidth="true" style="0"/>
+    <col min="9" max="9" width="24.7109375" customWidth="true" style="0"/>
+    <col min="10" max="10" width="21.140625" customWidth="true" style="0"/>
+    <col min="11" max="11" width="17.5703125" customWidth="true" style="0"/>
+    <col min="12" max="12" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" customHeight="1" ht="21.95">
       <c r="A1" s="8" t="s">
         <v>1129</v>
       </c>
@@ -24476,7 +24538,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>1136</v>
       </c>
@@ -24514,7 +24576,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>1178</v>
       </c>
@@ -24552,7 +24614,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>1202</v>
       </c>
@@ -24590,7 +24652,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
         <v>1223</v>
       </c>
@@ -24628,7 +24690,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>1245</v>
       </c>
@@ -24667,7 +24729,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:L1"/>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>